--- a/package-output-map.xlsx
+++ b/package-output-map.xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/floswald/git/JPEtemplate/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diegogonzalezgonzalez/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067DD2C7-24FE-2447-A5A8-8F6542C7C06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F1FE81-C5C7-5B4C-B5C8-4CF7574A8374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="21900" windowHeight="12060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="45">
   <si>
     <t>Data Preparation Program</t>
   </si>
@@ -45,20 +40,144 @@
     <t>Line Number</t>
   </si>
   <si>
+    <t>Figure 1</t>
+  </si>
+  <si>
+    <t>02_analysis.do</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Table 1</t>
+  </si>
+  <si>
+    <t>Figure 2</t>
+  </si>
+  <si>
+    <t>Table 2 (Panel A)</t>
+  </si>
+  <si>
+    <t>Table 2 (Panel B)</t>
+  </si>
+  <si>
+    <t>Table 3</t>
+  </si>
+  <si>
+    <t>Table 4</t>
+  </si>
+  <si>
+    <t>Table 5 (Panel A)</t>
+  </si>
+  <si>
+    <t>Table 5 (Panel B)</t>
+  </si>
+  <si>
+    <t>Table 6</t>
+  </si>
+  <si>
+    <t>Figure 3</t>
+  </si>
+  <si>
+    <t>Figure A1</t>
+  </si>
+  <si>
+    <t>Figure A2</t>
+  </si>
+  <si>
+    <t>Table A1</t>
+  </si>
+  <si>
+    <t>Table A2</t>
+  </si>
+  <si>
+    <t>Table A3 (Panel A)</t>
+  </si>
+  <si>
+    <t>Table A3 (Panel B)</t>
+  </si>
+  <si>
+    <t>Table A4</t>
+  </si>
+  <si>
+    <t>Table A5</t>
+  </si>
+  <si>
+    <t>Table A6</t>
+  </si>
+  <si>
+    <t>Table A7</t>
+  </si>
+  <si>
+    <t>Table A8</t>
+  </si>
+  <si>
     <t>In-text numbers</t>
+  </si>
+  <si>
+    <t>(Sec. 2.3)</t>
+  </si>
+  <si>
+    <t>(Footnote 17)</t>
+  </si>
+  <si>
+    <t>(Sec. 3.1)</t>
+  </si>
+  <si>
+    <t>(Sec. 3.2)</t>
+  </si>
+  <si>
+    <t>(Sec. 4, shares)</t>
+  </si>
+  <si>
+    <t>(Sec. 4, OLS)</t>
+  </si>
+  <si>
+    <t>(Footnote 24)</t>
+  </si>
+  <si>
+    <t>(Sec. 5.2–5.3)</t>
+  </si>
+  <si>
+    <t>(Footnote 27)</t>
+  </si>
+  <si>
+    <t>(Sec. 7.1)</t>
+  </si>
+  <si>
+    <t>(Footnote 30)</t>
+  </si>
+  <si>
+    <t>(Sec. 8, never-taker)</t>
+  </si>
+  <si>
+    <t>(Sec. 8, PRTE)</t>
+  </si>
+  <si>
+    <t>(Sec. 2.1 BCS numbers)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -66,7 +185,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -89,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -100,6 +218,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -118,7 +241,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -160,108 +283,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -269,80 +298,31 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -372,22 +352,22 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -402,51 +382,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" customWidth="1"/>
+    <col min="8" max="8" width="11.5" customWidth="1"/>
+    <col min="10" max="10" width="13.5" customWidth="1"/>
+    <col min="11" max="11" width="7.6640625" customWidth="1"/>
+    <col min="12" max="12" width="11.1640625" customWidth="1"/>
+    <col min="13" max="13" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -490,22 +445,525 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>130</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <v>182</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13">
+        <v>232</v>
+      </c>
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>279</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15">
+        <v>279</v>
+      </c>
+      <c r="D15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>494</v>
+      </c>
+      <c r="D16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17">
+        <v>610</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>702</v>
+      </c>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <v>702</v>
+      </c>
+      <c r="D19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <v>772</v>
+      </c>
+      <c r="D20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>860</v>
+      </c>
+      <c r="D21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22">
+        <v>889</v>
+      </c>
+      <c r="D22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>936</v>
+      </c>
+      <c r="D23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>943</v>
+      </c>
+      <c r="D24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25">
+        <v>975</v>
+      </c>
+      <c r="D25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26">
+        <v>1167</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>1167</v>
+      </c>
+      <c r="D27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28">
+        <v>1248</v>
+      </c>
+      <c r="D28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29">
+        <v>1322</v>
+      </c>
+      <c r="D29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30">
+        <v>1434</v>
+      </c>
+      <c r="D30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31">
+        <v>1459</v>
+      </c>
+      <c r="D31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>1719</v>
+      </c>
+      <c r="D32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C33" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D33" s="6" t="s">
         <v>2</v>
       </c>
     </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34">
+        <v>1883</v>
+      </c>
+      <c r="D34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35">
+        <v>1897</v>
+      </c>
+      <c r="D35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36">
+        <v>1897</v>
+      </c>
+      <c r="D36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37">
+        <v>1897</v>
+      </c>
+      <c r="D37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38">
+        <v>1933</v>
+      </c>
+      <c r="D38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39">
+        <v>1956</v>
+      </c>
+      <c r="D39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40">
+        <v>1998</v>
+      </c>
+      <c r="D40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41">
+        <v>2092</v>
+      </c>
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42">
+        <v>2150</v>
+      </c>
+      <c r="D42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43">
+        <v>2184</v>
+      </c>
+      <c r="D43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44">
+        <v>2196</v>
+      </c>
+      <c r="D44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45">
+        <v>2209</v>
+      </c>
+      <c r="D45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46">
+        <v>860</v>
+      </c>
+      <c r="D46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47">
+        <v>2229</v>
+      </c>
+      <c r="D47" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>